--- a/artfynd/A 55711-2024 artfynd.xlsx
+++ b/artfynd/A 55711-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2914463</v>
+        <v>67384644</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>3739</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klackberg, Vstm</t>
+          <t>Klackbergs NR, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549344.9105676567</v>
+        <v>549476</v>
       </c>
       <c r="R2" t="n">
-        <v>6660169.733506258</v>
+        <v>6660295</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-07-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-07-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,18 +757,134 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Blandskog med gran,tall,björk och asp</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>I mossa</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Lars Bsenko</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Lars Bsenko</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2914463</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Klackberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>549345</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6660170</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2007-07-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2007-07-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Per Hedenbo</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Kurt Svanberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Regional miljöövervakning</t>
         </is>

--- a/artfynd/A 55711-2024 artfynd.xlsx
+++ b/artfynd/A 55711-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67384644</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,8 +899,17 @@
           <t>Regional miljöövervakning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2914463</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>